--- a/archivos-incremento-1/Grupo1 - Organización de trabajo.xlsx
+++ b/archivos-incremento-1/Grupo1 - Organización de trabajo.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jbmv7\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{931BA2E8-F9A3-40AB-91D2-2541F14D4F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6EEB938-2ACB-41F9-9C8C-E3775355C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pila del Producto" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="182">
   <si>
     <t>PILA DEL PRODUCTO</t>
   </si>
@@ -124,9 +123,6 @@
   </si>
   <si>
     <t>Diagramas de secuencia Módulo 1 (CU-01 a CU-12)</t>
-  </si>
-  <si>
-    <t>Javiera Moran, Vicente Abarca</t>
   </si>
   <si>
     <t>Definir flujo de autenticación, gestión de usuarios y auditoría</t>
@@ -577,6 +573,18 @@
   </si>
   <si>
     <t>Creación del PPT para la presentación del incremento 1</t>
+  </si>
+  <si>
+    <t>Javier Farías,  Vicente Abarca, Javiera Morán</t>
+  </si>
+  <si>
+    <t>Javier Farías,  Uriel Navarrete</t>
+  </si>
+  <si>
+    <t>Javier Farías,  Fabiola Oses</t>
+  </si>
+  <si>
+    <t>Por no participacion se desvinculó a Kenji Kimura del proyecto.</t>
   </si>
 </sst>
 </file>
@@ -586,7 +594,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,14 +636,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -698,12 +698,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -842,11 +842,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -857,12 +872,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -875,19 +890,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -923,86 +938,92 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1019,6 +1040,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1228,48 +1253,48 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="55" customWidth="1"/>
     <col min="6" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" style="27" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="26" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="41" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="34" t="s">
+      <c r="G1" s="39"/>
+      <c r="H1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="49" t="s">
+      <c r="I1" s="49"/>
+      <c r="J1" s="47" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="46" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="35" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="49"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="47"/>
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1306,18 +1331,18 @@
       <c r="K3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="A4" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -1330,7 +1355,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>16</v>
@@ -1353,7 +1378,7 @@
     </row>
     <row r="6" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -1362,7 +1387,7 @@
         <v>50</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
@@ -1394,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>21</v>
@@ -1414,7 +1439,7 @@
       <c r="J7" s="3">
         <v>2</v>
       </c>
-      <c r="K7" s="28"/>
+      <c r="K7" s="27"/>
     </row>
     <row r="8" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -1427,7 +1452,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>24</v>
@@ -1449,20 +1474,20 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="30">
+      <c r="B9" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="29">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>174</v>
+        <v>170</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>173</v>
       </c>
       <c r="F9" s="19">
         <v>46186</v>
@@ -1481,34 +1506,34 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
       <c r="C11" s="9">
         <v>8</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="16">
         <v>46147</v>
@@ -1528,22 +1553,22 @@
     </row>
     <row r="12" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="C12" s="3">
         <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="17" t="s">
         <v>32</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>33</v>
       </c>
       <c r="G12" s="17">
         <v>46180</v>
@@ -1560,22 +1585,22 @@
     </row>
     <row r="13" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>179</v>
       </c>
       <c r="C13" s="3">
         <v>8</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>36</v>
       </c>
       <c r="G13" s="17">
         <v>46180</v>
@@ -1592,22 +1617,22 @@
     </row>
     <row r="14" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>179</v>
       </c>
       <c r="C14" s="3">
         <v>8</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G14" s="19">
         <v>46180</v>
@@ -1624,22 +1649,22 @@
     </row>
     <row r="15" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="C15" s="7">
         <v>5</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>41</v>
       </c>
       <c r="G15" s="19">
         <v>46180</v>
@@ -1655,40 +1680,40 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
+      <c r="A16" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>44</v>
       </c>
       <c r="C17" s="9">
         <v>5</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>18</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>18</v>
@@ -1702,25 +1727,25 @@
     </row>
     <row r="18" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="3">
         <v>5</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>18</v>
@@ -1734,19 +1759,19 @@
     </row>
     <row r="19" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C19" s="7">
         <v>10</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>17</v>
@@ -1765,22 +1790,22 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
+      <c r="A20" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
     </row>
     <row r="21" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>15</v>
@@ -1789,10 +1814,10 @@
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F21" s="16">
         <v>46183</v>
@@ -1812,30 +1837,30 @@
     </row>
     <row r="22" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="30">
+        <v>169</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="29">
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F22" s="19">
+      <c r="F22" s="51">
         <v>46184</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="51">
         <v>45454</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="51">
         <v>45453</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="51">
         <v>46184</v>
       </c>
       <c r="J22" s="7">
@@ -1844,19 +1869,19 @@
     </row>
     <row r="23" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="7">
         <v>4</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" s="16">
         <v>46183</v>
@@ -1875,34 +1900,34 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
+      <c r="A24" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
     </row>
     <row r="25" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="9">
+        <v>2</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="C25" s="9">
-        <v>2</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="F25" s="16">
         <v>46186</v>
@@ -1922,19 +1947,19 @@
     </row>
     <row r="26" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F26" s="16">
         <v>46186</v>
@@ -1954,19 +1979,19 @@
     </row>
     <row r="27" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F27" s="16">
         <v>46186</v>
@@ -1985,34 +2010,34 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
+      <c r="A28" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
     </row>
     <row r="29" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="9">
+        <v>2</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="9">
-        <v>2</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>68</v>
       </c>
       <c r="F29" s="16">
         <v>46171</v>
@@ -2032,19 +2057,19 @@
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="3">
-        <v>2</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="F30" s="16">
         <v>46171</v>
@@ -2064,19 +2089,19 @@
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="3">
+        <v>2</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C31" s="3">
-        <v>2</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="F31" s="16">
         <v>46171</v>
@@ -2096,19 +2121,19 @@
     </row>
     <row r="32" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="3">
-        <v>2</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="F32" s="16">
         <v>46171</v>
@@ -2128,19 +2153,19 @@
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="3">
-        <v>2</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="F33" s="16">
         <v>46171</v>
@@ -2160,19 +2185,19 @@
     </row>
     <row r="34" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="3">
-        <v>2</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="F34" s="16">
         <v>46171</v>
@@ -2192,19 +2217,19 @@
     </row>
     <row r="35" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="3">
-        <v>2</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="F35" s="16">
         <v>46171</v>
@@ -2224,19 +2249,19 @@
     </row>
     <row r="36" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="3">
-        <v>2</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="F36" s="16">
         <v>46171</v>
@@ -2256,19 +2281,19 @@
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="3">
-        <v>2</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="F37" s="16">
         <v>46171</v>
@@ -2288,19 +2313,19 @@
     </row>
     <row r="38" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="3">
-        <v>2</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="F38" s="16">
         <v>46171</v>
@@ -2320,19 +2345,19 @@
     </row>
     <row r="39" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="3">
-        <v>2</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="F39" s="16">
         <v>46171</v>
@@ -2352,19 +2377,19 @@
     </row>
     <row r="40" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="7">
-        <v>2</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="F40" s="16">
         <v>46171</v>
@@ -2383,34 +2408,34 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
+      <c r="A41" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="46"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
     </row>
     <row r="42" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="9">
+        <v>2</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="9">
-        <v>2</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>94</v>
       </c>
       <c r="F42" s="16">
         <v>46174</v>
@@ -2430,19 +2455,19 @@
     </row>
     <row r="43" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="3">
+        <v>2</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="3">
-        <v>2</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F43" s="16">
         <v>46174</v>
@@ -2462,19 +2487,19 @@
     </row>
     <row r="44" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="3">
-        <v>2</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="F44" s="16">
         <v>46174</v>
@@ -2494,19 +2519,19 @@
     </row>
     <row r="45" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="3">
+        <v>2</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="3">
-        <v>2</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F45" s="16">
         <v>46174</v>
@@ -2526,19 +2551,19 @@
     </row>
     <row r="46" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="3">
+        <v>2</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" s="3">
-        <v>2</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="F46" s="16">
         <v>46174</v>
@@ -2558,19 +2583,19 @@
     </row>
     <row r="47" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="3">
+        <v>2</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="3">
-        <v>2</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="F47" s="16">
         <v>46174</v>
@@ -2590,19 +2615,19 @@
     </row>
     <row r="48" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" s="3">
+        <v>2</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" s="3">
-        <v>2</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="F48" s="16">
         <v>46174</v>
@@ -2622,19 +2647,19 @@
     </row>
     <row r="49" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="3">
+        <v>2</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" s="3">
-        <v>2</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="F49" s="16">
         <v>46174</v>
@@ -2654,19 +2679,19 @@
     </row>
     <row r="50" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="3">
+        <v>2</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" s="3">
-        <v>2</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="F50" s="16">
         <v>46174</v>
@@ -2686,19 +2711,19 @@
     </row>
     <row r="51" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="3">
+        <v>2</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51" s="3">
-        <v>2</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="F51" s="16">
         <v>46174</v>
@@ -2718,19 +2743,19 @@
     </row>
     <row r="52" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="7">
+        <v>2</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="7">
-        <v>2</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="F52" s="16">
         <v>46174</v>
@@ -2749,34 +2774,34 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" s="33"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="33"/>
+      <c r="A53" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" s="46"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="46"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="46"/>
     </row>
     <row r="54" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="C54" s="9">
+        <v>2</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="C54" s="9">
-        <v>2</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="F54" s="16">
         <v>46176</v>
@@ -2796,19 +2821,19 @@
     </row>
     <row r="55" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="3">
+        <v>2</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C55" s="3">
-        <v>2</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="F55" s="16">
         <v>46176</v>
@@ -2828,19 +2853,19 @@
     </row>
     <row r="56" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="3">
+        <v>2</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C56" s="3">
-        <v>2</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F56" s="16">
         <v>46176</v>
@@ -2860,19 +2885,19 @@
     </row>
     <row r="57" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" s="3">
+        <v>2</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" s="3">
-        <v>2</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F57" s="16">
         <v>46176</v>
@@ -2892,19 +2917,19 @@
     </row>
     <row r="58" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C58" s="3">
-        <v>2</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="F58" s="16">
         <v>46176</v>
@@ -2924,19 +2949,19 @@
     </row>
     <row r="59" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" s="3">
+        <v>2</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="3">
-        <v>2</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="F59" s="16">
         <v>46176</v>
@@ -2956,19 +2981,19 @@
     </row>
     <row r="60" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" s="3">
+        <v>2</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C60" s="3">
-        <v>2</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="F60" s="16">
         <v>46176</v>
@@ -2988,19 +3013,19 @@
     </row>
     <row r="61" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C61" s="7">
+        <v>2</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="7">
-        <v>2</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="F61" s="16">
         <v>46176</v>
@@ -3019,34 +3044,34 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" s="33"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="33"/>
-      <c r="J62" s="33"/>
+      <c r="A62" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" s="46"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
+      <c r="G62" s="46"/>
+      <c r="H62" s="46"/>
+      <c r="I62" s="46"/>
+      <c r="J62" s="46"/>
     </row>
     <row r="63" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" s="9">
+        <v>2</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E63" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C63" s="9">
-        <v>2</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>135</v>
       </c>
       <c r="F63" s="16">
         <v>46176</v>
@@ -3066,19 +3091,19 @@
     </row>
     <row r="64" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C64" s="3">
+        <v>2</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C64" s="3">
-        <v>2</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="F64" s="16">
         <v>46176</v>
@@ -3098,19 +3123,19 @@
     </row>
     <row r="65" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C65" s="3">
+        <v>2</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C65" s="3">
-        <v>2</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F65" s="16">
         <v>46176</v>
@@ -3130,19 +3155,19 @@
     </row>
     <row r="66" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C66" s="3">
+        <v>2</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C66" s="3">
-        <v>2</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F66" s="16">
         <v>46176</v>
@@ -3162,19 +3187,19 @@
     </row>
     <row r="67" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C67" s="3">
+        <v>2</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C67" s="3">
-        <v>2</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F67" s="16">
         <v>46176</v>
@@ -3194,19 +3219,19 @@
     </row>
     <row r="68" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" s="3">
+        <v>2</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C68" s="3">
-        <v>2</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="F68" s="16">
         <v>46176</v>
@@ -3226,19 +3251,19 @@
     </row>
     <row r="69" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C69" s="3">
+        <v>2</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C69" s="3">
-        <v>2</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F69" s="16">
         <v>46176</v>
@@ -3258,19 +3283,19 @@
     </row>
     <row r="70" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C70" s="3">
+        <v>2</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C70" s="3">
-        <v>2</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="F70" s="16">
         <v>46176</v>
@@ -3290,19 +3315,19 @@
     </row>
     <row r="71" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" s="7">
+        <v>2</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C71" s="7">
-        <v>2</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="F71" s="16">
         <v>46176</v>
@@ -3321,34 +3346,34 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="B72" s="33"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
+      <c r="A72" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="46"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46"/>
+      <c r="J72" s="46"/>
     </row>
     <row r="73" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="C73" s="9">
+        <v>2</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="C73" s="9">
-        <v>2</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>155</v>
       </c>
       <c r="F73" s="16">
         <v>46178</v>
@@ -3368,19 +3393,19 @@
     </row>
     <row r="74" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="3">
+        <v>2</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C74" s="3">
-        <v>2</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="F74" s="16">
         <v>46178</v>
@@ -3400,19 +3425,19 @@
     </row>
     <row r="75" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C75" s="3">
+        <v>2</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C75" s="3">
-        <v>2</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="F75" s="16">
         <v>46178</v>
@@ -3432,19 +3457,19 @@
     </row>
     <row r="76" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C76" s="3">
+        <v>2</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C76" s="3">
-        <v>2</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="F76" s="16">
         <v>46178</v>
@@ -3464,19 +3489,19 @@
     </row>
     <row r="77" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77" s="3">
+        <v>2</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C77" s="3">
-        <v>2</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="F77" s="16">
         <v>46178</v>
@@ -3496,19 +3521,19 @@
     </row>
     <row r="78" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C78" s="3">
+        <v>2</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C78" s="3">
-        <v>2</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="F78" s="16">
         <v>46178</v>
@@ -3527,34 +3552,34 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="B79" s="33"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="33"/>
-      <c r="E79" s="33"/>
-      <c r="F79" s="33"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="33"/>
-      <c r="J79" s="33"/>
+      <c r="A79" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="46"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="46"/>
+      <c r="F79" s="46"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="46"/>
+      <c r="I79" s="46"/>
+      <c r="J79" s="46"/>
     </row>
     <row r="80" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="C80" s="3">
         <v>3</v>
       </c>
-      <c r="D80" s="52" t="s">
-        <v>171</v>
-      </c>
-      <c r="E80" s="29" t="s">
-        <v>178</v>
+      <c r="D80" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="E80" s="28" t="s">
+        <v>177</v>
       </c>
       <c r="F80" s="16">
         <v>46181</v>
@@ -3573,26 +3598,57 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="B81" s="37"/>
+      <c r="A81" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" s="34"/>
       <c r="C81" s="1">
         <f>SUM(C5:C80)</f>
         <v>230</v>
       </c>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="32"/>
-      <c r="J81" s="26">
+      <c r="D81" s="1">
+        <f>SUM(D5:D80)</f>
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
+        <f>SUM(E5:E80)</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
+        <f>SUM(F5:F80)</f>
+        <v>2631960</v>
+      </c>
+      <c r="G81" s="1">
+        <f>SUM(G5:G80)</f>
+        <v>2863062.0416666665</v>
+      </c>
+      <c r="H81" s="1">
+        <f>SUM(H5:H80)</f>
+        <v>2815838</v>
+      </c>
+      <c r="I81" s="1">
+        <f>SUM(I5:I80)</f>
+        <v>3001580</v>
+      </c>
+      <c r="J81" s="1">
         <f>SUM(J5:J80)</f>
         <v>219</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="53"/>
+      <c r="C82" s="53"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="53"/>
+      <c r="I82" s="53"/>
+      <c r="J82" s="54"/>
+    </row>
     <row r="83" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="85" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4514,7 +4570,11 @@
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A82:J82"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -4531,20 +4591,8 @@
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02568C0-024F-4D18-8E56-0DFDF47CBAF6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>